--- a/SubClase/UOcc_SubClase.xlsx
+++ b/SubClase/UOcc_SubClase.xlsx
@@ -680,13 +680,13 @@
         <v>1.227558384100949</v>
       </c>
       <c r="C2" s="2">
-        <v>107.8388784691189</v>
+        <v>107.8836663667572</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.323785193968102</v>
+        <v>1.324334991560624</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -711,7 +711,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>5.352374763938658</v>
+        <v>5.352374763938659</v>
       </c>
       <c r="C4" s="2">
         <v>121.1749102131284</v>
@@ -1221,10 +1221,10 @@
         <v>38</v>
       </c>
       <c r="B34" s="2">
-        <v>5.042006659206553</v>
+        <v>5.042006659206554</v>
       </c>
       <c r="C34" s="2">
-        <v>125.8079265802694</v>
+        <v>125.8079265802693</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>6</v>
@@ -1527,7 +1527,7 @@
         <v>56</v>
       </c>
       <c r="B52" s="2">
-        <v>0.8636908479485087</v>
+        <v>0.8636908479485086</v>
       </c>
       <c r="C52" s="2">
         <v>104.9136347401929</v>
@@ -1544,7 +1544,7 @@
         <v>57</v>
       </c>
       <c r="B53" s="2">
-        <v>0.9815194703490917</v>
+        <v>0.9815194703490916</v>
       </c>
       <c r="C53" s="2">
         <v>105.3377160937909</v>
@@ -1578,7 +1578,7 @@
         <v>59</v>
       </c>
       <c r="B55" s="2">
-        <v>0.9710206158672994</v>
+        <v>0.9710206158672995</v>
       </c>
       <c r="C55" s="2">
         <v>106.0139722125379</v>
@@ -1649,13 +1649,13 @@
         <v>2.704200202707706</v>
       </c>
       <c r="C59" s="2">
-        <v>113.1121544917801</v>
+        <v>113.1121544917802</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E59" s="2">
-        <v>3.058779111053772</v>
+        <v>3.058779111053773</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1867,7 +1867,7 @@
         <v>76</v>
       </c>
       <c r="B72" s="2">
-        <v>0.703675755262945</v>
+        <v>0.7036757552629451</v>
       </c>
       <c r="C72" s="2">
         <v>120.0770669376348</v>
